--- a/education_forms/039_research_publication_support_request_form--education_forms.xlsx
+++ b/education_forms/039_research_publication_support_request_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Research Publication Support Request Form</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>research_group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Research Group</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>research_group</t>
+          <t>research_publication_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>research_group</t>
+          <t>Research Publication Type</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>research_publication_type</t>
+          <t>manuscript_status</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>research_publication_type</t>
+          <t>Manuscript Status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>manuscript_status</t>
+          <t>manuscript_status_details</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>manuscript_status</t>
+          <t>Manuscript Status Details</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>manuscript_status_details</t>
+          <t>manuscript_format</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>manuscript_status_details</t>
+          <t>Manuscript Format</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>manuscript_format</t>
+          <t>manuscript_length</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>manuscript_format</t>
+          <t>Manuscript Length</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>manuscript_length</t>
+          <t>manuscript_language</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>manuscript_length</t>
+          <t>Manuscript Language</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>manuscript_language</t>
+          <t>manuscript_format_details</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>manuscript_language</t>
+          <t>Manuscript Format Details</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>manuscript_format_details</t>
+          <t>attachments_required</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>manuscript_format_details</t>
+          <t>Attachments Required</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_comments</t>
+          <t>attachments_comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_comments</t>
+          <t>Attachments Comments</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments_comments</t>
+          <t>attachments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments_comments</t>
+          <t>Attachments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments</t>
+          <t>assigned_to</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments</t>
+          <t>Assigned To</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_comments</t>
+          <t>assigned_date</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_comments</t>
+          <t>Assigned Date</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments</t>
+          <t>assigned_time</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments</t>
+          <t>Assigned Time</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>assigned_by</t>
+          <t>status_update</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>assigned_by</t>
+          <t>Status Update</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>assigned_date</t>
+          <t>due_date</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>assigned_date</t>
+          <t>Due Date</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>assigned_time</t>
+          <t>due_time</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>assigned_time</t>
+          <t>Due Time</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,90 +998,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>status_update</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>status_update</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>due_date</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>due_date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>due_time</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>due_time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1029,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>research_article</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Research Article</t>
         </is>
       </c>
     </row>
@@ -1148,316 +1079,384 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>research_report</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Research Report</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>research_publication_type_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>research_publication_type_choices</t>
+          <t>research_group_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>research_group_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Research Group A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>manuscript_status_choices</t>
+          <t>research_group_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>research_group_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Research Group B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>manuscript_status_choices</t>
+          <t>research_group_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>manuscript_format_choices</t>
+          <t>research_publication_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>research_article</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Research Article</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>manuscript_format_choices</t>
+          <t>research_publication_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>research_report</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Research Report</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>manuscript_language_choices</t>
+          <t>research_publication_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>manuscript_language_choices</t>
+          <t>manuscript_status_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments_choices</t>
+          <t>manuscript_status_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments_choices</t>
+          <t>manuscript_format_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments_choices</t>
+          <t>manuscript_format_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments_choices</t>
+          <t>manuscript_language_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments_choices</t>
+          <t>manuscript_language_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>research_publication_support_request_form_attachments_choices</t>
+          <t>attachments_required_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>attachments_required_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>attachments_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>attachments_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>assigned_to_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>user_a</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>User A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>assigned_to_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>user_b</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>User B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assigned_to_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>status_choices</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>status_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>inactive</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
